--- a/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_1/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,71 +471,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Access Requirement; Availability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>La arquitectura implementada para el desarrollo del sistema del proyecto Revivack es una arquitectura basada en microservicios. La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí. En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6381</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
 directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M08_C10</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Responsiveness</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Traefik acts as a reverse proxy and load balancer, improving the availability and responsiveness of the application.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7261</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M08_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -543,26 +543,26 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Security; Integrity</t>
+          <t>Responsiveness</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, improving the availability and responsiveness of the application.</t>
+          <t>Puerto443(HTTPS) :Traefikabreelpuerto443paramanejartráficoHTTPS,queesel estándar para comunicaciones seguras en la web. HTTPS cifra los datos transmitidos entre los clientes y el servidor, protegiendo la integridad y confidencialidad de la información.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.5949</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -601,16 +601,16 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6263</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="5">
@@ -649,16 +649,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7456</v>
+        <v>0.7020999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -697,16 +697,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers an additional structure, features and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7246</v>
+        <v>0.6147</v>
       </c>
     </row>
     <row r="7">
@@ -745,16 +745,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.677</v>
+        <v>0.7244</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -793,16 +793,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6975</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="9">
@@ -841,16 +841,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, which promotes modularity, code reuse, and maintainability.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions [...] para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7342</v>
+        <v>0.6435999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -889,32 +889,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM [...] Prisma Client es una biblioteca de consultas generada automáticamente para realizar operaciones con bases de datos. Proporciona una API para crear, leer, actualizar y eliminar datos en la base de datos.</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7812</v>
+        <v>0.6754</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Depuration</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -937,16 +937,112 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>System Service (Next.js) [...] Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM [...] Prisma Client es una biblioteca de consultas generada automáticamente para realizar operaciones con bases de datos. Proporciona una API para crear, leer, actualizar y eliminar datos en la base de datos.</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.7723</v>
+        <v>0.7242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CF_M08_C06</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P05</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Adaptability requirements</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Singleton</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>La arquitectura implementada para el desarrollo del sistema del proyecto Revivack es una arquitectura basada en microservicios. La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí. En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Modularity; Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Component-based</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>La arquitectura implementada para el desarrollo del sistema del proyecto Revivack es una arquitectura basada en microservicios. La arquitectura de software basada en microservicios es un enfoque de diseño y desarrollo de software donde una aplicación se construye como una colección de servicios pequeños e independientes que se comunican entre sí. En el caso de esta aplicación, dichos servicios se ejecutan en instancias de Amazon EC2 y son gestionados por Docker, que administra la ejecución de los contenedores.</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6768</v>
       </c>
     </row>
   </sheetData>
